--- a/group_project/Phase_2_Project_Proposal/phase_2_table.xlsx
+++ b/group_project/Phase_2_Project_Proposal/phase_2_table.xlsx
@@ -99,9 +99,7 @@
   </si>
   <si>
     <t xml:space="preserve">Use at least one or two paragraphs to deeply describe each SOTA method that you mention in Section 1. For example, 
-if there are three SOTA methods listed in Section 1, you should have at least  three paragraphs, i.e., one paragraph for 
-each method. Please also re-state what advantages of those methods are and why those methods should be able to address 
-the problem</t>
+if there are three SOTA methods listed in Section 1, you should have at least  three paragraphs, i.e., one paragraph for each method. Please also re-state what advantages of those methods are and why those methods should be able to address the problem</t>
   </si>
   <si>
     <t xml:space="preserve">Section 3. Proposed High-level Solution and Process (At Least 3 Pages) (8 Points) </t>
@@ -110,15 +108,10 @@
     <t xml:space="preserve">3 Pages</t>
   </si>
   <si>
-    <t xml:space="preserve">In this section, you need to describe and explain your proposed high-level solution and process to solve the problem using 
-the SOTA methods in detail. You may include, but are not limited to: 
-▪  A workflow/pipeline diagram to show the entire solution and process, using the SOTA methods, and describe/explain 
-them in detail. 
-▪  Your development and implementation for your workflow/pipeline with the SOTA methods. That is, what libraries, 
-modules, classes,  functions, etc., have been implemented and used to address your solution and process described 
-above based on your workflow/pipeline. 
-▪  Please include any mathematical models, pseudocode algorithms, python code implementations, etc., to support your 
-workflow/pipeline development and implementation</t>
+    <t xml:space="preserve">In this section, you need to describe and explain your proposed high-level solution and process to solve the problem using the SOTA methods in detail. You may include, but are not limited to: 
+▪  A workflow/pipeline diagram to show the entire solution and process, using the SOTA methods, and describe/explain them in detail. 
+▪  Your development and implementation for your workflow/pipeline with the SOTA methods. That is, what libraries, modules, classes,  functions, etc., have been implemented and used to address your solution and process described above based on your workflow/pipeline. 
+▪  Please include any mathematical models, pseudocode algorithms, python code implementations, etc., to support your workflow/pipeline development and implementation</t>
   </si>
   <si>
     <t xml:space="preserve">Section 4. Preliminary Experimental Results and Discussions (At Least 1 Page) (2 Points) </t>
@@ -127,10 +120,8 @@
     <t xml:space="preserve">1 page</t>
   </si>
   <si>
-    <t xml:space="preserve">▪  In this section, you need to describe how you will measure the performance or success  of your proposed high-level 
-solution and process using the SOTA methods in detail. 
-▪  What  data,  experiments,  demo,  and/or  prototypes  will  you  use  and  conduct,  respectively,  to  assure  that  your 
-approach(es) are really performing and successful? Please describe them in detail. 
+    <t xml:space="preserve">▪  In this section, you need to describe how you will measure the performance or success  of your proposed high-level solution and process using the SOTA methods in detail. 
+▪  What  data,  experiments,  demo,  and/or  prototypes  will  you  use  and  conduct,  respectively,  to  assure  that  your approach(es) are really performing and successful? Please describe them in detail. 
 ▪  Your preliminary experimental results should include MOST SOTA methods for the performance comparisons. 
 ▪  You can use tables, charts, pictures, etc., to show your preliminary experimental results and provide discussions.</t>
   </si>
@@ -336,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -367,6 +358,9 @@
     <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -944,38 +938,38 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" ht="99.75">
+    <row r="6" ht="71.25">
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="13" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" ht="213.75">
+    <row r="7" ht="142.5">
       <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="13" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" ht="142.5">
+    <row r="8" ht="114">
       <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="13" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="11"/>
@@ -993,16 +987,16 @@
       <c r="E9" s="11"/>
     </row>
     <row r="10" ht="42.75">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="17"/>
+      <c r="E10" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/group_project/Phase_2_Project_Proposal/phase_2_table.xlsx
+++ b/group_project/Phase_2_Project_Proposal/phase_2_table.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Links:</t>
   </si>
@@ -145,6 +146,12 @@
   <si>
     <t xml:space="preserve">Use the Gantt chart to draw up a timeline schedule to lay out all the identified, remaining project work tasks from the 
 above to be undertaken for the rest of the semester week by week. </t>
+  </si>
+  <si>
+    <t>NN</t>
+  </si>
+  <si>
+    <t>Ephocs</t>
   </si>
 </sst>
 </file>
@@ -969,7 +976,7 @@
       <c r="C8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="11"/>
@@ -1011,4 +1018,27 @@
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="19.421875"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
 </file>